--- a/results/previous_signals.xlsx
+++ b/results/previous_signals.xlsx
@@ -550,10 +550,10 @@
         <v>57.11340206185567</v>
       </c>
       <c r="I2" t="n">
-        <v>21.52534935291033</v>
+        <v>21.52534935291669</v>
       </c>
       <c r="J2" t="n">
-        <v>7.823164239493314</v>
+        <v>7.823164239502628</v>
       </c>
       <c r="K2" t="n">
         <v>60.42857142857143</v>
@@ -736,10 +736,10 @@
         <v>72.76595744680851</v>
       </c>
       <c r="I5" t="n">
-        <v>131.9546460466877</v>
+        <v>131.9546460466904</v>
       </c>
       <c r="J5" t="n">
-        <v>112.9971908529266</v>
+        <v>112.9971908529313</v>
       </c>
       <c r="K5" t="n">
         <v>108</v>
@@ -868,10 +868,10 @@
         <v>68.5714379135545</v>
       </c>
       <c r="I7" t="n">
-        <v>1.058512313680836</v>
+        <v>1.058512313681064</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6646264775032666</v>
+        <v>0.664626477503624</v>
       </c>
       <c r="K7" t="n">
         <v>2.092857360839844</v>
@@ -992,10 +992,10 @@
         <v>32.9339378238342</v>
       </c>
       <c r="I9" t="n">
-        <v>-330.8487271337945</v>
+        <v>-330.8487271338236</v>
       </c>
       <c r="J9" t="n">
-        <v>1211.043838637597</v>
+        <v>1211.043838637554</v>
       </c>
       <c r="K9" t="n">
         <v>4185</v>
@@ -1054,10 +1054,10 @@
         <v>52.29202037351443</v>
       </c>
       <c r="I10" t="n">
-        <v>433.7060962678825</v>
+        <v>433.7060962678588</v>
       </c>
       <c r="J10" t="n">
-        <v>524.4440499884445</v>
+        <v>524.4440499884098</v>
       </c>
       <c r="K10" t="n">
         <v>387.8571428571428</v>
@@ -1116,10 +1116,10 @@
         <v>45.4383464005702</v>
       </c>
       <c r="I11" t="n">
-        <v>-43.71144526283751</v>
+        <v>-43.71144526284388</v>
       </c>
       <c r="J11" t="n">
-        <v>5.097338162817163</v>
+        <v>5.097338162808551</v>
       </c>
       <c r="K11" t="n">
         <v>302.2142857142857</v>
